--- a/artfynd/A 14729-2023 artfynd.xlsx
+++ b/artfynd/A 14729-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 14729-2023 artfynd.xlsx
+++ b/artfynd/A 14729-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>72532249</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -717,10 +712,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>672569.7735709422</v>
+        <v>672570</v>
       </c>
       <c r="R2" t="n">
-        <v>6556996.129460959</v>
+        <v>6556996</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,19 +745,9 @@
           <t>2018-07-31</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-07-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -795,59 +780,47 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>72532296</v>
+        <v>72532282</v>
       </c>
       <c r="B3" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sågstugan, S om, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>672602.1952314508</v>
+        <v>672602</v>
       </c>
       <c r="R3" t="n">
-        <v>6556973.944032471</v>
+        <v>6556974</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -877,24 +850,14 @@
           <t>2018-07-31</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-07-31</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Gnagspår på tallgren som fallit till marken.</t>
+          <t>På granlåga.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,52 +885,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>72532282</v>
+        <v>72532222</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4781</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>102306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sågstugan, S om, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>672602.1952314508</v>
+        <v>672560</v>
       </c>
       <c r="R4" t="n">
-        <v>6556973.944032471</v>
+        <v>6557013</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -997,24 +962,9 @@
           <t>2018-07-31</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2018-07-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På granlåga.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,6 +989,118 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>72532296</v>
+      </c>
+      <c r="B5" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sågstugan, S om, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>672602</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6556974</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Västerhaninge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2018-07-31</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2018-07-31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gnagspår på tallgren som fallit till marken.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14729-2023 artfynd.xlsx
+++ b/artfynd/A 14729-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72532249</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72532282</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -989,6 +1004,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72532222</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1101,8 +1121,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72532296</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>